--- a/dataset/construct/dataset_splits/data_size/2_percent/merged/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/2_percent/merged/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1079</v>
+        <v>2158</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,91 +625,91 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.0231582249601</v>
+        <v>88.0696089056202</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>29.3877551020408</v>
       </c>
       <c r="E2" t="n">
-        <v>24.2809753428405</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>157.2</v>
       </c>
       <c r="I2" t="n">
-        <v>928</v>
+        <v>177.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>280.7</v>
       </c>
       <c r="K2" t="n">
-        <v>800</v>
+        <v>615.3</v>
       </c>
       <c r="L2" t="n">
-        <v>544</v>
+        <v>64.2</v>
       </c>
       <c r="M2" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1783</v>
+        <v>52.8</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="P2" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>98</v>
+        <v>22.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>28.615991851286</v>
       </c>
       <c r="X2" t="n">
-        <v>23.3</v>
+        <v>27.2921406849679</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.299270072992701</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.050433101168</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -733,30 +718,19 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>170</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,82 +738,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>71.47246748802191</v>
+        <v>85.0743345501559</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>25.5593291551416</v>
       </c>
       <c r="E3" t="n">
-        <v>24.1671624033313</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>903.7</v>
       </c>
       <c r="I3" t="n">
-        <v>587</v>
+        <v>809.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>747.3</v>
       </c>
       <c r="K3" t="n">
-        <v>168.7</v>
+        <v>2460.6</v>
       </c>
       <c r="L3" t="n">
-        <v>83</v>
+        <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>128.9</v>
+        <v>58.9</v>
       </c>
       <c r="N3" t="n">
-        <v>380.6</v>
+        <v>146.1</v>
       </c>
       <c r="O3" t="n">
-        <v>23.7</v>
+        <v>211.1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>36.3</v>
+        <v>63.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>24.7</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.7962821492233</v>
       </c>
       <c r="X3" t="n">
-        <v>25.15</v>
+        <v>24.4717629124263</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.277397260273973</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.3692386045327</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.7150115381059</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -851,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -860,25 +834,18 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>93</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>146</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55739338</v>
+        <v>51803581</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,74 +853,86 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.28815879534569</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>87.233401779603</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29.7056440723738</v>
+      </c>
       <c r="E4" t="n">
-        <v>27.7551020408163</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>445</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>546</v>
+      </c>
+      <c r="L4" t="n">
+        <v>445</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
       <c r="O4" t="n">
-        <v>470.93115</v>
+        <v>546</v>
       </c>
       <c r="P4" t="n">
-        <v>325.70068</v>
+        <v>377</v>
       </c>
       <c r="Q4" t="n">
-        <v>114.440186</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>911.0721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>26.51521351910976</v>
       </c>
       <c r="X4" t="n">
-        <v>26.807087</v>
+        <v>25.9429069949188</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>84.35317000000001</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>540.5214</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -965,30 +944,17 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>137</v>
-      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54908834</v>
+        <v>51646767</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -996,71 +962,85 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.2231348391513</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>71.65776865160851</v>
+      </c>
+      <c r="D5" t="n">
+        <v>29.4758426246316</v>
+      </c>
       <c r="E5" t="n">
-        <v>29.7619047619048</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>60</v>
+      </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>55</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I5" t="n">
+        <v>192</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="K5" t="n">
+        <v>411</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" t="n">
+        <v>108</v>
+      </c>
+      <c r="N5" t="n">
+        <v>102</v>
+      </c>
       <c r="O5" t="n">
-        <v>482</v>
+        <v>223</v>
       </c>
       <c r="P5" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>726</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1709</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>130</v>
+        <v>23.4</v>
       </c>
       <c r="V5" t="n">
-        <v>137</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.30563595161136</v>
       </c>
       <c r="X5" t="n">
-        <v>30.1</v>
+        <v>23.98436212016794</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>99.3</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>660.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1080,21 +1060,8 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>150</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
